--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N32_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N32_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.361394492717406</v>
+        <v>1.033726605066579</v>
       </c>
       <c r="D2" t="n">
-        <v>5.362786080333055</v>
+        <v>0.8714527380541214</v>
       </c>
       <c r="E2" t="n">
-        <v>15.24987250006003</v>
+        <v>2.478104281259755</v>
       </c>
       <c r="F2" t="n">
-        <v>18.12222160178696</v>
+        <v>2.944861010290381</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3.851237625750974</v>
+        <v>0.6258261141845333</v>
       </c>
       <c r="D3" t="n">
-        <v>4.656546484326974</v>
+        <v>0.7566888037031333</v>
       </c>
       <c r="E3" t="n">
-        <v>15.24987250006003</v>
+        <v>2.478104281259755</v>
       </c>
       <c r="F3" t="n">
-        <v>18.12222160178696</v>
+        <v>2.944861010290381</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>40.78964320396299</v>
+        <v>6.628317020643986</v>
       </c>
       <c r="D4" t="n">
-        <v>51.84868735180917</v>
+        <v>8.425411694668989</v>
       </c>
       <c r="E4" t="n">
-        <v>15.24987250006003</v>
+        <v>2.478104281259755</v>
       </c>
       <c r="F4" t="n">
-        <v>18.12222160178696</v>
+        <v>2.944861010290381</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.90343785063731</v>
+        <v>5.671808650728563</v>
       </c>
       <c r="D5" t="n">
-        <v>34.23163590868057</v>
+        <v>5.562640835160592</v>
       </c>
       <c r="E5" t="n">
-        <v>15.24987250006003</v>
+        <v>2.478104281259755</v>
       </c>
       <c r="F5" t="n">
-        <v>18.12222160178696</v>
+        <v>2.944861010290381</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.85703379357613</v>
+        <v>5.014267991456122</v>
       </c>
       <c r="D6" t="n">
-        <v>31.12476998961603</v>
+        <v>5.057775123312605</v>
       </c>
       <c r="E6" t="n">
-        <v>15.24987250006003</v>
+        <v>2.478104281259755</v>
       </c>
       <c r="F6" t="n">
-        <v>18.12222160178696</v>
+        <v>2.944861010290381</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
